--- a/www/download/COUNTRY.EST.EXI382.xlsx
+++ b/www/download/COUNTRY.EST.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Estônia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.08038834355828</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.08038834355828</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.08038834355828</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.08038834355828</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.08038834355828</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.08038834355828</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.08038834355828</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0800490797546</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1.312</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.642</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.615</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.616</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.557</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.595</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.596</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.604</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.622</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.659</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.664</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.655</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.593</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.567</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.603</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.614</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.639</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.614</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0.636</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0.675</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.691</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.763</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.826</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>0.843</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1.222</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.594</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.564</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.558</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.559</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.506</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.545</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.542</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.552</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.553</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.551</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.572</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.604</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.603</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.603</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.543</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.519</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.582</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0.561</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0.615</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>0.694</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.751</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>0.767</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2624.057</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1287.36</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1226.864</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1222.093</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1241.477</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1156.999</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1196.229</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1182.544</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1197.808</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1188.383</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1222.234</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1265.252</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1339.137</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1349.415</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1345.608</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1172.661</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1146.707</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1223.029</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1236.751</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1277.521</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>1216.715</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1253.191</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>1326.554</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1356.757</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>1494.572</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>1616.92</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1644.894</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2452.01</t>
+          <t>2755869364.87196</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1079.21</t>
+          <t>2751103371.69079</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1010.778</t>
+          <t>2424349916.72315</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1000.963</t>
+          <t>2662170984.46117</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>995.141</t>
+          <t>2581640069.89023</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>930.136</t>
+          <t>3299724715.46642</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>986.949</t>
+          <t>2924054703.6615</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>977.552</t>
+          <t>2713196769.75891</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1011.718</t>
+          <t>2590118973.09673</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>979.287</t>
+          <t>2819118291.98534</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>981.078</t>
+          <t>2799164293.29329</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1053.596</t>
+          <t>3009080887.97734</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1224.73</t>
+          <t>2755840541.69627</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1221.132</t>
+          <t>2934393701.89708</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1239.102</t>
+          <t>2250322144.19318</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1074.69</t>
+          <t>2571032963.58824</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1050.721</t>
+          <t>2334533610.59422</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1115.046</t>
+          <t>2539207357.59107</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1126.911</t>
+          <t>2495941121.68389</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1162.089</t>
+          <t>2385605769.27635</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>1109.894</t>
+          <t>2417045950.81807</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>1141.746</t>
+          <t>2252939202.26466</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1208.665</t>
+          <t>2257322873.47809</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1236.614</t>
+          <t>2577969098.18575</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1360.584</t>
+          <t>2677384283.66219</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>1469.568</t>
+          <t>2830264254.92</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1495.462</t>
+          <t>2932237128.10686</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>898016872.75452</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>857436680.965258</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>819274106.22806</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>778116210.396263</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>697590602.729899</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>731632982.283988</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>635565505.543878</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>794648842.967498</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>843396463.376348</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>501489981.694448</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>574430606.222263</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>951352748.328834</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>820333389.950043</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1056814753.44278</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1056047763.0686</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1097259625.36654</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>755602354.228377</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1097275485.35982</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>977345349.104979</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>768464806.716001</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>603699241.722142</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>843421663.979202</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>791351717.657795</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>859299636.090849</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>791379276.199803</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>982569998.502914</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>670929493.363358</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>74074838.2079192</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>49341045.4889407</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>34430881.0338309</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>37706185.1241515</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>33501699.6716116</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>44002858.2994542</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30161196.5477063</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>26492639.5002055</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>43949950.2058042</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>62149363.9738077</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>17124874.3468131</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>20121705.4474471</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>101016186.961048</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>13084678.670302</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>12442142.8294664</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>15961631.5767153</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>9718679.27537175</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>8628420.74073616</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>8976284.83479966</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>147592160.538528</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>154191169.93625</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>102774753.912019</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>98049130.7963428</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>127347030.350976</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>132311532.615817</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>134687492.06293</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>9621941.5849223</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6961.86472799434</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6776.90632568447</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>7058.26632567561</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7119.49542201611</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>7419.66597503075</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>8269.35011244891</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8484.37303595003</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>8051.70875111187</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7012.43466813219</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6991.14140450321</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>7678.24681140434</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>8569.03280506405</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>9459.40522770702</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>9599.66626960265</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>9439.23360700455</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>9431.54679587108</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>9342.54352809343</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>11289.7058026199</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>11172.0682304526</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>11421.0779077095</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>12806.4266025654</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>11579.2811224714</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>12711.7932432182</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12917.8379241187</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>14606.232688867</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14899.5186998771</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>15059.6464892529</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10272.7859242263</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20905.8337828706</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>20065.4327508485</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>22652.2558942805</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>23170.9808147966</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>35402.1309729452</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>31500.114642451</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>28332.9281884233</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>24846.4455006833</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>26427.6039407023</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>28130.9623127892</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>32348.5520641339</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>30694.3098509145</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>32840.2950756681</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>25237.6983749914</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>33252.0942111352</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>31432.8860343421</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>37736.0470181667</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>36233.5254697901</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>35846.6820623664</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>41027.2936106765</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>34856.2086684058</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>36923.2348653947</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>41011.5046064365</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>45381.3175196466</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>45636.4743316935</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>46419.2494870437</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.73047192847357</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.258646876157911</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.233748256311767</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.286392683542675</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.426540145617837</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.271315020676707</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.552867472181633</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.230168531233889</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.19957581509181</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.952754862003249</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.707913870488453</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.107471441955188</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.492966170832957</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.155483490386536</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.173338975123145</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.0205690839661498</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.390574015710965</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.0161951259071955</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.153032549888572</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.512221981308601</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.838488479504039</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.353707440188743</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.527341854458176</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.439095582735475</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.719256531837487</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.495636784369546</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.2289406140943</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>734.930163278877</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1444.46880216532</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1451.84140745714</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1393.97386312479</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1248.81955375937</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1447.05890483382</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1166.8175244061</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1466.68298812736</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1527.06221867893</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>907.67417501239</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1041.76751219115</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1663.78584877376</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1357.04448296125</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1752.30434993009</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1751.90405286759</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2019.99194655095</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1454.76001969252</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1995.7720723163</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1745.88308164481</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1320.86487291066</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1076.84805904952</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1455.31462258186</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1287.35901791058</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1364.95069568739</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1139.96257970742</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1308.83942511271</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>875.294897492812</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>360906810.183706</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>512702360.312819</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>458261159.969739</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>323246762.931701</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>384087552.687838</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>408710966.062519</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>427922807.482344</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>512141149.357336</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>927418178.163975</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>260458745.08746</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>204698585.473993</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>574118588.067374</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>324671323.055125</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>598091331.347076</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>659746863.15762</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>952456561.60096</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>568633720.186252</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>899346802.671849</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>749109645.396393</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>532592626.629914</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>401343235.628093</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>559284465.817936</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>575748600.507321</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>681042173.238774</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>642136663.344051</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>740733293.034842</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>289003857.992267</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>340903181.111559</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>489400618.686545</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>406294134.604126</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>290468707.331332</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>360406095.435233</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>385189979.784394</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>365171469.847045</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>475068703.643</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>900031692.27636</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>239842945.426684</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>161221352.993726</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>511756277.176387</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>270509907.520417</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>505500807.554653</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>550055273.424775</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>821877581.768155</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>397900511.358925</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>725876676.441999</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>570488754.180791</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>336664665.267183</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>251678387.919042</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>385837199.339604</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>410043781.748343</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>489740281.520833</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>431209750.742103</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>536695173.054967</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>890780120.929461</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>20003629.0721468</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>23301741.6262745</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>51967025.365613</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>32778055.6003686</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>23681457.252605</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>23520986.2781247</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>62751337.6352998</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>37072445.7143364</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>27386485.8876157</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>20615799.6607758</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>43477232.4802668</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>62362310.890987</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>54161415.5347086</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>92590523.7924227</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>109691589.732845</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>130578979.832805</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>170733208.827327</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>173470126.22985</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>178620891.215602</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>195927961.362731</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>149664847.709051</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>173447266.478331</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>165704818.758978</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>191301891.717941</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>210926912.601948</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>204038119.979875</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-601776262.937194</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2006.70618022147</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1818.07614555294</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1791.20680489147</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1793.19777857345</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1781.4912280703</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1839.66772151922</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1811.91297962173</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1804.26725729037</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1831.82690566768</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1772.46515837023</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1779.24918389551</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>1842.59531304611</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>2026.02150537665</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>2024.75874647673</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>2055.57730590575</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1978.44256259139</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>2022.95148247958</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>2028.09385230952</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>2013.06002143623</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>1997.44089515389</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1979.77275073884</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>1970.07023240454</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>1966.23730976901</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>1964.29451681543</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1959.88811121229</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>1957.54838903166</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1950.98034633123</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2000.50952750651</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2003.67315175133</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1993.28025995153</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2003.75963272622</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2014.07689811801</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2075.33452914801</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2011.82139253268</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2003.29324072486</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2008.73385879643</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1968.499254596</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2005.30598851525</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2033.84021861405</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2031.14970423206</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2030.72234762997</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2055.61869844181</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1977.50590219156</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2022.05431140877</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2029.58679057382</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2013.92444227327</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1998.68375184884</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1981.11268171678</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1971.12278493283</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1966.5563686281</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1964.2546644532</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1959.48854783611</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1957.04961348344</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1950.30605718582</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2487.07915961321</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2268.88069536807</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3196.46660451671</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>3716.61541986663</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3892.20555396065</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3682.88687988839</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4334.99819444703</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>4409.69023492965</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>4560.5615906791</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>5374.26451458767</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>6527.53068505493</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>7600.22734502579</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>8745.2751371801</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>9771.74776441416</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>8353.05135545212</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>10708.1492033797</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>15410.858512127</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>17384.5309391404</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>17589.0672824987</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>19325.3122910591</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>19290.6632270379</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>20207.6141408633</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>21561.9774229886</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>23304.244189648</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>24609.8037871583</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>25479.2829162711</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>25404.9956354964</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>797064184.752932</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>812856571.303057</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>753626796.658698</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>931656864.52165</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>861296603.943839</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>954704247.090295</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>880939064.324562</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>788703974.777687</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>693411814.65078</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>779752941.072854</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>850326722.640658</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>837548750.091622</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>735710084.47339</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>879524874.875456</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>703797180.498041</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>915511986.938982</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>928197897.878433</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1061760447.85852</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1055749198.26847</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>999322571.811291</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>1024245921.36107</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>1008288147.83614</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>988907775.891893</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>1120439328.53386</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1133498127.33937</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>1231443512.99655</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1192136842.63219</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2814.4135380114</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2794.78454854977</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3815.31657400457</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>4348.8223169713</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>4203.49399384744</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3946.18655722237</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4699.61091797071</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>5171.08724783752</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>5526.92419810137</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6376.61726364955</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>7282.90092016839</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>9399.42287120631</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>10637.2918401009</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>10620.4092525165</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>7437.22990787057</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>9470.85976022321</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>14144.1319430284</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>16996.5084435886</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>16925.4736364459</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>18411.5031514223</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>18229.5076129601</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>19182.4274431267</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>20336.8184159886</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>22421.3846176146</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>23143.0742372915</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>24344.3101883138</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>24570.7044761274</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2624.057</t>
+          <t>1343414509.45458</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1287.36</t>
+          <t>1432390014.2165</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1226.864</t>
+          <t>1327729069.69788</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1222.093</t>
+          <t>1374010345.09314</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1241.477</t>
+          <t>1302488119.84567</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1156.999</t>
+          <t>1404263677.38193</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1196.229</t>
+          <t>1367666243.07223</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1182.544</t>
+          <t>1428252389.83386</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1197.808</t>
+          <t>1784993408.46642</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1188.383</t>
+          <t>1224032998.0879</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1222.234</t>
+          <t>1181361421.31283</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1265.252</t>
+          <t>1679372698.40149</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1339.137</t>
+          <t>1295336590.13953</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1349.415</t>
+          <t>1593916224.45294</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1345.608</t>
+          <t>1228742993.49222</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1172.661</t>
+          <t>1715408265.34718</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1146.707</t>
+          <t>1350758086.98167</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1223.029</t>
+          <t>1918800679.97321</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1236.751</t>
+          <t>1728841831.23428</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1277.521</t>
+          <t>1434771719.47766</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>1216.715</t>
+          <t>1323012673.28272</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>1253.191</t>
+          <t>1458844868.1051</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>1326.554</t>
+          <t>1446645683.05333</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>1356.757</t>
+          <t>1713734348.3322</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>1494.572</t>
+          <t>1641770189.22042</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>1616.92</t>
+          <t>1862037547.05176</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1644.894</t>
+          <t>1399851479.78554</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2452.01</t>
+          <t>-327.334378398196</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1079.21</t>
+          <t>-525.903853181698</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1010.778</t>
+          <t>-618.849969487861</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1000.963</t>
+          <t>-632.206897104673</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>995.141</t>
+          <t>-311.28843988679</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>930.136</t>
+          <t>-263.299677333984</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>986.949</t>
+          <t>-364.612723523682</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>977.552</t>
+          <t>-761.397012907871</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1011.718</t>
+          <t>-966.362607422279</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>979.287</t>
+          <t>-1002.35274906188</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>981.078</t>
+          <t>-755.370235113461</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1053.596</t>
+          <t>-1799.19552618052</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1224.73</t>
+          <t>-1892.0167029208</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1221.132</t>
+          <t>-848.66148810237</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1239.102</t>
+          <t>915.821447581549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1074.69</t>
+          <t>1237.28944315648</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1050.721</t>
+          <t>1266.7265690985</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1115.046</t>
+          <t>388.022495551743</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1126.911</t>
+          <t>663.593646052825</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1162.089</t>
+          <t>913.809139636791</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>1109.894</t>
+          <t>1061.15561407785</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>1141.746</t>
+          <t>1025.18669773657</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>1208.665</t>
+          <t>1225.15900700005</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>1236.614</t>
+          <t>882.859572033425</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1360.584</t>
+          <t>1466.72954986679</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>1469.568</t>
+          <t>1134.97272795731</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>1495.462</t>
+          <t>834.291159369001</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1860.899</t>
+          <t>-546350324.701646</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1878.979</t>
+          <t>-619533442.913443</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1691.274</t>
+          <t>-574102273.039185</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1846.016</t>
+          <t>-442353480.571494</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1761.881</t>
+          <t>-441191515.901827</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2138.028</t>
+          <t>-449559430.291637</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1938.697</t>
+          <t>-486727178.747673</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1829.984</t>
+          <t>-639548415.056176</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1736.916</t>
+          <t>-1091581593.81564</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1870.101</t>
+          <t>-444280057.015042</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1856.972</t>
+          <t>-331034698.672176</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1994.711</t>
+          <t>-841823948.309871</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1884.174</t>
+          <t>-559626505.666136</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1978.697</t>
+          <t>-714391349.57748</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1576.766</t>
+          <t>-524945812.994177</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1755.021</t>
+          <t>-799896278.408201</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1581.475</t>
+          <t>-422560189.103238</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1738.011</t>
+          <t>-857040232.114697</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1710.062</t>
+          <t>-673092632.965807</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1641.268</t>
+          <t>-435449147.666366</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>1653.736</t>
+          <t>-298766751.921649</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>1558.317</t>
+          <t>-450556720.26897</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>1577.361</t>
+          <t>-457737907.161438</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1773.563</t>
+          <t>-593295019.798331</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1844.347</t>
+          <t>-508272061.881047</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>1958.007</t>
+          <t>-630594034.055208</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1991.612</t>
+          <t>-207714637.153347</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1501.80305849292</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1719.28451845484</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2209.51271758629</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2192.92616938142</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2156.5279807475</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>2451.02341210783</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2513.77362019528</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>2775.02290538314</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>3312.76685463371</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>3257.65810049945</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>4164.41022103905</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>5006.13488059624</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>6124.75570633522</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>6299.08179816878</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>6108.13920664859</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>5512.02139201122</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>6757.71182003411</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>6764.85793885819</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>6860.90888538391</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>7606.9040075673</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>7678.22663559125</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>8144.41476049831</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>8627.14806928807</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>8739.13183549924</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>9159.28475805614</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>9492.96724242565</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>10039.1530074576</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1867.652</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>891.807</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>852.795</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>836.708</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>826.677</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>770.761</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>787.577</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>771.042</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>731.012</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>745.768</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>764.022</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>797.096</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>849.298</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>857.763</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>841.65</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>729.242</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>693.875</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>759.669</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>769.586</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>760.076</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>754.467</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>748.43</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>777.143</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>812.011</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>861.731</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>924.032</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>951.296</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2167.9752341741</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2343.72159400129</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>3060.77854650594</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>3041.03505838252</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2976.87933263442</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3588.11012417577</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3583.78419802002</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>4351.83788420848</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>4983.73857715163</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>4842.55383232829</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6215.58801241625</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7609.14608361905</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9495.13702806671</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>10002.6500586918</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9196.92272624815</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8619.72920313491</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>10157.124899463</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10464.1498668138</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11415.2710565818</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11620.2312973966</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12259.5220705441</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>13736.8168844295</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>13941.8686318838</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>15635.5085505895</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>16722.1281414158</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>17061.356644428</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>17825.6438403032</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>784.532</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>765.555</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>794.045</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>739.006</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>655.705</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>659.458</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>583.299</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>742.848</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>793.83</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>448.939</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>513.617</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>908.137</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>761.536</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>997.909</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1019.11</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1052.06</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>702.468</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1064.891</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>948.819</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>737.737</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>572.38</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>816.382</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>766.882</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>828.111</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>762.342</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>943.326</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>626.039</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>212.54</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>40.97</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>27.29</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>35.45</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>51.77</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>41.05</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>69.2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>27.45</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>118.13</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>91.01</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>16.02</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>60.82</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>22.37</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>21.59</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>49.58</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>4.71</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>18.77</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>57.52</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>93.91</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>57.61</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>49.33</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>78.47</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>55.79</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>138.88</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>68.51</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>44.681</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>31.353</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>34.935</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>30.397</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>38.622</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>26.955</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>23.964</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>44.102</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>64.807</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>15.291</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>18.663</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>110.76</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>11.56</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>11.294</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>14.441</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>8.677</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>7.89</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>163.33</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>170.734</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>113.249</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>108.289</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>140.889</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>146.416</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>149.271</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>8.808</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1163.38230074322</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1329.42822641259</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1463.81470579033</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1972.75577328244</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2380.90210531652</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2510.12350785905</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3293.90453279257</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>3380.75898822799</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>3802.99372175603</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>4952.41580861385</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>5231.34044295039</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>6116.37495337821</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>7258.39963940248</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>6934.5277213869</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>5076.95782769346</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>6449.90044845956</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>6628.821159844</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>7613.24162761521</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>7945.2210637924</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>8860.67954622709</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>8988.5913481077</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>8706.11347047362</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>10547.6192431051</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10855.6877750819</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>12078.1634684866</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12548.4828343701</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>12871.0678856739</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2452009862.35184</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1079210000.00013</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1010778000.00025</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1000962999.99971</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>995140999.999945</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>930136000.00013</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>986948999.999764</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>977552000.000037</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1011718000.00023</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>979286999.999754</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>981078000.000094</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1053595999.99976</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1224730000.00013</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1221132000.00005</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1239102000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1074689999.99971</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1050721000.00001</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1115046000.0001</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1126911000.00025</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1162089372.578</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>1109894100.99148</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>1141746181.74502</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>1208664599.97612</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>1236614310.54454</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>1360583989.76733</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>1469567832.97889</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>1495461996.9513</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2624056679.20521</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1287360000.00011</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1226864000.00016</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1222092999.99974</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1241476999.99979</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1156998999.99997</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1196228999.99974</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1182544000.00002</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1197808000.0003</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1188382999.99983</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1222234000.00017</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1265251999.9998</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1339137000.00013</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1349415000.00004</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1345608000</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1172660999.99969</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1146707000.00001</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1223029000.0001</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1236751000.00027</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1277521014.85041</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>1216714733.50015</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>1253191474.66119</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1326553638.66803</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>1356757367.59699</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>1494571895.72668</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>1616920043.81368</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1644893727.35019</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1867652053.47228</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>891807044.668045</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>852795331.719812</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>836707576.717821</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>826676571.848375</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>770760917.40764</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>787577161.701979</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>771041737.347937</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>731011608.120402</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>745767745.706854</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>764022007.871548</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>797096351.980397</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>849297884.639422</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>857763311.106996</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>841650300.056815</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>729241820.254717</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>693874620.705989</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>759668971.825539</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>769586291.952021</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>760075627.099415</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>754466571.88532</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>748429544.447415</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>777142678.73463</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>812010856.546908</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>861731214.122537</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>924032274.826461</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>951296176.907745</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1311694.16747338</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>642499.999999938</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>615499.999999996</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>609900.00000001</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>616399.999999925</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>557499.999999977</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>594599.999999903</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>590300.000000069</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>596299.999999995</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>603700.000000114</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>609500.000000063</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>622100.000000003</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>659299.999999969</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>664499.99999996</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>654599.999999997</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>593000.000000048</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>567100.000000046</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>602600.000000155</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>614100.000000125</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>639181.167940485</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>614157.258559257</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>635775.449525789</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>674556.63098712</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>690723.7600857</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>762735.713549925</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>826202.888610295</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>843402.870687734</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1221907.7643351</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>593599.999999948</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>564299.999999998</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>558200.000000003</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>558599.99999993</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>505600.000000006</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>544699.999999895</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>541800.000000065</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>552299.999999985</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>552500.000000113</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>551400.000000061</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>571799.999999999</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>604499.999999976</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>603099.999999966</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>602800.00000001</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>543200.000000033</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>519400.000000058</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>549800.000000159</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>559800.000000124</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>581789.115962037</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>560616.919581946</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>579545.928345649</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>614709.421884642</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>629546.282371839</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>694215.135029185</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>750718.521806677</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>766518.227497</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2624056679.20521</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1287360000.00011</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1226864000.00016</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1222092999.99974</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1241476999.99979</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1156998999.99997</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1196228999.99974</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1182544000.00002</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1197808000.0003</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1188382999.99983</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1222234000.00017</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1265251999.9998</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1339137000.00013</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1349415000.00004</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1345608000</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1172660999.99969</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1146707000.00001</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1223029000.0001</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1236751000.00027</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1277521014.85041</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>1216714733.50015</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>1253191474.66119</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>1326553638.66803</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>1356757367.59699</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>1494571895.72668</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>1616920043.81368</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1644893727.35019</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2452009862.35184</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1079210000.00013</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1010778000.00025</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1000962999.99971</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>995140999.999945</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>930136000.00013</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>986948999.999764</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>977552000.000037</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1011718000.00023</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>979286999.999754</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>981078000.000094</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1053595999.99976</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1224730000.00013</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1221132000.00005</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1239102000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1074689999.99971</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1050721000.00001</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1115046000.0001</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1126911000.00025</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1162089372.578</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>1109894100.99148</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>1141746181.74502</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>1208664599.97612</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>1236614310.54454</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>1360583989.76733</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>1469567832.97889</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1495461996.9513</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>8043.87289613303</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>8760.2753962796</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>10782.2072462326</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>11967.6807728505</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>12451.8099100244</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>14630.3631015085</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>15926.5167391027</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>17806.899023183</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>19068.3786727012</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>21204.0984891961</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>24499.9104493946</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>29342.2062660499</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>34814.6980647248</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>35232.1202879327</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>28737.8087240939</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>32024.2771132468</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>38238.3094371377</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>41378.8588872986</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>43185.3420465759</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>43605.9236174888</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>44478.8273408168</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>46701.7368743369</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>50108.7747737238</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>54970.8271496297</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>59701.742776127</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>60780.227422708</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>63209.4217592055</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2493.96320206664</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2698.17050070333</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3394.70406861015</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3435.49941169986</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3410.75815817332</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>4094.00704317307</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4181.30291714862</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>4963.47067623324</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>5536.00005679018</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>5492.49704696846</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>6885.48786610167</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>8383.17522350598</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>10269.1501111067</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>10767.2688974591</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>10070.1710040397</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>9448.67981628369</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>11362.8167380888</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>11710.3057004458</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>12420.1502917095</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>12707.9667398408</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>13237.5595519225</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>14737.8662324974</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>14971.6543872427</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16876.8554311544</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>17987.0377854774</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>18388.4266766552</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>18927.2228107651</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
